--- a/templates/deliverable/example/05_DB표준단어.xlsx
+++ b/templates/deliverable/example/05_DB표준단어.xlsx
@@ -29,25 +29,25 @@
     <t>표준단어명</t>
   </si>
   <si>
-    <t>단어영문명</t>
-  </si>
-  <si>
-    <t>단어영문약어명</t>
-  </si>
-  <si>
-    <t>단어설명</t>
-  </si>
-  <si>
-    <t>형식단어여부</t>
-  </si>
-  <si>
-    <t>도메인분류명</t>
-  </si>
-  <si>
-    <t>이음동의어목록</t>
-  </si>
-  <si>
-    <t>금칙어목록</t>
+    <t>단어 영문명</t>
+  </si>
+  <si>
+    <t>단어 영문약어명</t>
+  </si>
+  <si>
+    <t>단어 설명</t>
+  </si>
+  <si>
+    <t>형식단어 여부</t>
+  </si>
+  <si>
+    <t>도메인 분류명</t>
+  </si>
+  <si>
+    <t>이음동의어 목록</t>
+  </si>
+  <si>
+    <t>금칙어 목록</t>
   </si>
   <si>
     <t>관리부서명</t>
@@ -74,12 +74,12 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="11.0"/>
+      <sz val="14.0"/>
       <b val="true"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="14.0"/>
+      <sz val="11.0"/>
       <b val="true"/>
     </font>
   </fonts>
@@ -133,8 +133,8 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFont="true" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="true"/>
   </cellXfs>
 </styleSheet>
@@ -149,13 +149,13 @@
     <col min="2" max="2" width="10.0" customWidth="true"/>
     <col min="3" max="3" width="10.0" customWidth="true"/>
     <col min="4" max="4" width="14.0" customWidth="true"/>
-    <col min="5" max="5" width="14.0" customWidth="true"/>
-    <col min="6" max="6" width="18.0" customWidth="true"/>
-    <col min="7" max="7" width="12.0" customWidth="true"/>
-    <col min="8" max="8" width="16.0" customWidth="true"/>
-    <col min="9" max="9" width="16.0" customWidth="true"/>
-    <col min="10" max="10" width="18.0" customWidth="true"/>
-    <col min="11" max="11" width="14.0" customWidth="true"/>
+    <col min="5" max="5" width="16.0" customWidth="true"/>
+    <col min="6" max="6" width="20.0" customWidth="true"/>
+    <col min="7" max="7" width="14.0" customWidth="true"/>
+    <col min="8" max="8" width="18.0" customWidth="true"/>
+    <col min="9" max="9" width="18.0" customWidth="true"/>
+    <col min="10" max="10" width="20.0" customWidth="true"/>
+    <col min="11" max="11" width="16.0" customWidth="true"/>
     <col min="12" max="12" width="14.0" customWidth="true"/>
     <col min="13" max="13" width="12.0" customWidth="true"/>
     <col min="14" max="14" width="12.0" customWidth="true"/>
